--- a/kortdata/F_personkort.xlsx
+++ b/kortdata/F_personkort.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -703,7 +703,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Starkt kontaktnät</t>
+          <t>Inhyrd jurist</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Inhyrd jurist</t>
+          <t>Branschens bäste</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>+2 på ett förhandlingsslag. Spelas före slaget.</t>
+          <t>+3 på ett förhandlingsslag. Spelas före slaget.</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
@@ -764,7 +764,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>forhandling_mod</t>
+          <t>forhandling_auto</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -772,19 +772,15 @@
           <t>fore_slag</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Övertaget läge</t>
+          <t>Signerat på plats</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>+2 på ett förhandlingsslag. Spelas före slaget.</t>
+          <t>Vinn en förhandling automatiskt.</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
@@ -802,7 +798,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>forhandling_mod</t>
+          <t>forhandling_auto</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -810,19 +806,15 @@
           <t>fore_slag</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
+      <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Branschens bäste</t>
+          <t>Oemotståndligt bud</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>+3 på ett förhandlingsslag. Spelas före slaget.</t>
+          <t>Vinn en förhandling automatiskt.</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
@@ -840,7 +832,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>forhandling_mod</t>
+          <t>forhandling_auto</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -848,19 +840,15 @@
           <t>fore_slag</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Motpartens svaghet</t>
+          <t>Fast handslag</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>+3 på ett förhandlingsslag. Spelas före slaget.</t>
+          <t>Vinn en förhandling automatiskt.</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
@@ -878,23 +866,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>forhandling_auto</t>
+          <t>energi_mod</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>fore_slag</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t>efter_slag</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Signerat på plats</t>
+          <t>Bättre isolering</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Vinn en förhandling automatiskt.</t>
+          <t>+1 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
@@ -912,23 +904,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>forhandling_auto</t>
+          <t>energi_mod</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>fore_slag</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>efter_slag</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Oemotståndligt bud</t>
+          <t>Injusterat system</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Vinn en förhandling automatiskt.</t>
+          <t>+1 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
@@ -946,23 +942,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>forhandling_auto</t>
+          <t>energi_mod</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>fore_slag</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>efter_slag</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Fast handslag</t>
+          <t>Energikonsult inhyrd</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Vinn en förhandling automatiskt.</t>
+          <t>+2 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
@@ -990,17 +990,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Bättre isolering</t>
+          <t>Erfaren installatör</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>+1 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
+          <t>+2 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Injusterat system</t>
+          <t>Statligt stöd hittat</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>+1 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
+          <t>+2 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Extra timme på plats</t>
+          <t>Certifierad expert</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>+1 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
+          <t>+3 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
@@ -1104,17 +1104,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Rätt verktyg</t>
+          <t>Helhetslösning levererad</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>+1 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
+          <t>+3 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
@@ -1132,27 +1132,23 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>energi_mod</t>
+          <t>lagg_dn_plus_egen</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>efter_slag</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
+          <t>nar_som_helst</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Energikonsult inhyrd</t>
+          <t>Dold förbättring</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>+2 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
+          <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
@@ -1170,27 +1166,23 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>energi_mod</t>
+          <t>lagg_dn_plus_egen</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>efter_slag</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
+          <t>nar_som_helst</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Erfaren installatör</t>
+          <t>Tyst uppgradering</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>+2 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
+          <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
@@ -1208,27 +1200,23 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>energi_mod</t>
+          <t>lagg_dn_plus_egen</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>efter_slag</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
+          <t>nar_som_helst</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Statligt stöd hittat</t>
+          <t>Extra underhåll</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>+2 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
+          <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
@@ -1246,27 +1234,23 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>energi_mod</t>
+          <t>lagg_dn_plus_egen</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>efter_slag</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
+          <t>nar_som_helst</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Noggrann besiktning</t>
+          <t>Kvalitetshöjning</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>+2 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
+          <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
@@ -1284,27 +1268,23 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>energi_mod</t>
+          <t>lagg_dn_plus_egen</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>efter_slag</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
+          <t>nar_som_helst</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Certifierad expert</t>
+          <t>Diskret investering</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>+3 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
+          <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
@@ -1322,27 +1302,23 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>energi_mod</t>
+          <t>lagg_dn_plus_egen</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>efter_slag</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
+          <t>nar_som_helst</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Helhetslösning levererad</t>
+          <t>Renoverat i tysthet</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>+3 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
+          <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
@@ -1371,7 +1347,7 @@
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Dold förbättring</t>
+          <t>Fastighetsskötarens tips</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1405,7 +1381,7 @@
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Tyst uppgradering</t>
+          <t>Väl skött förvaltning</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1428,7 +1404,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>lagg_dn_plus_egen</t>
+          <t>stada</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1439,12 +1415,12 @@
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Extra underhåll</t>
+          <t>Problemet är löst</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
+          <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
@@ -1462,7 +1438,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>lagg_dn_plus_egen</t>
+          <t>stada</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1473,12 +1449,12 @@
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Kvalitetshöjning</t>
+          <t>Snabb insats</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
+          <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
@@ -1496,7 +1472,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>lagg_dn_plus_egen</t>
+          <t>stada</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1507,12 +1483,12 @@
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Diskret investering</t>
+          <t>Städat upp</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
+          <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
@@ -1530,7 +1506,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>lagg_dn_plus_egen</t>
+          <t>stada</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1541,12 +1517,12 @@
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Renoverat i tysthet</t>
+          <t>Åtgärdat i tid</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
+          <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
@@ -1564,7 +1540,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>lagg_dn_plus_egen</t>
+          <t>stada</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1575,12 +1551,12 @@
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Fastighetsskötarens tips</t>
+          <t>Krisen avvärjd</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
+          <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
@@ -1598,7 +1574,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>lagg_dn_plus_egen</t>
+          <t>stada</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1609,12 +1585,12 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Väl skött förvaltning</t>
+          <t>Rent bord igen</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
+          <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
@@ -1632,23 +1608,23 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>stada</t>
+          <t>stopp</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>nar_som_helst</t>
+          <t>reaktivt</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Problemet är löst</t>
+          <t>Hembudsrätt använd</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
+          <t>Avvärj ett fientligt bud på en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
@@ -1666,23 +1642,23 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>stada</t>
+          <t>stopp</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>nar_som_helst</t>
+          <t>reaktivt</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Snabb insats</t>
+          <t>Motbud i sista minuten</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
+          <t>Avvärj ett fientligt bud på en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
@@ -1700,23 +1676,23 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>stada</t>
+          <t>stopp</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>nar_som_helst</t>
+          <t>reaktivt</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Städat upp</t>
+          <t>Låst avtal</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
+          <t>Avvärj ett fientligt bud på en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
@@ -1734,23 +1710,23 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>stada</t>
+          <t>stopp</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>nar_som_helst</t>
+          <t>reaktivt</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Åtgärdat i tid</t>
+          <t>Styrelsen säger nej</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
+          <t>Avvärj ett fientligt bud på en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
@@ -1768,23 +1744,23 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>stada</t>
+          <t>stopp</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>nar_som_helst</t>
+          <t>reaktivt</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Krisen avvärjd</t>
+          <t>Juridiskt hinder</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
+          <t>Avvärj ett fientligt bud på en av dina fastigheter.</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
@@ -1802,7 +1778,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>stada</t>
+          <t>kika</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1813,12 +1789,12 @@
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Rent bord igen</t>
+          <t>Tips från branschen</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
+          <t>Titta på ett dolt kort hos en motståndare.</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
@@ -1836,23 +1812,23 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>stopp</t>
+          <t>kika</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>reaktivt</t>
+          <t>nar_som_helst</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Hembudsrätt använd</t>
+          <t>Insyn i affären</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Avvärj ett fientligt bud på en av dina fastigheter.</t>
+          <t>Titta på ett dolt kort hos en motståndare.</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
@@ -1870,23 +1846,23 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>stopp</t>
+          <t>kika</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>reaktivt</t>
+          <t>nar_som_helst</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Motbud i sista minuten</t>
+          <t>Bra rykte i huset</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Avvärj ett fientligt bud på en av dina fastigheter.</t>
+          <t>Titta på ett dolt kort hos en motståndare.</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
@@ -1904,23 +1880,23 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>stopp</t>
+          <t>kika</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>reaktivt</t>
+          <t>nar_som_helst</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Låst avtal</t>
+          <t>Läckt information</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Avvärj ett fientligt bud på en av dina fastigheter.</t>
+          <t>Titta på ett dolt kort hos en motståndare.</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
@@ -1938,23 +1914,23 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>stopp</t>
+          <t>hyresgastvarvning</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>reaktivt</t>
+          <t>nar_som_helst</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Styrelsen säger nej</t>
+          <t>Bättre villkor lockar över hyresgästen</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Avvärj ett fientligt bud på en av dina fastigheter.</t>
+          <t>En hyresgäst hos en konkurrent flyttar till er efter ett bättre erbjudande. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
@@ -1972,23 +1948,23 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>stopp</t>
+          <t>hyresgastvarvning</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>reaktivt</t>
+          <t>nar_som_helst</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Juridiskt hinder</t>
+          <t>Vi tar ankarhyresgästen</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Avvärj ett fientligt bud på en av dina fastigheter.</t>
+          <t>Er uthyrare vinner en stor hyresgäst som konkurrenten räknat med. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
@@ -2006,7 +1982,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>kika</t>
+          <t>hyresgastvarvning</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2017,12 +1993,12 @@
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Tips från branschen</t>
+          <t>Flytterbjudande med hyresrabatt</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Titta på ett dolt kort hos en motståndare.</t>
+          <t>Tre månaders rabatt räcker för att hyresgästen byter hyresvärd. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
@@ -2040,7 +2016,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>kika</t>
+          <t>hyresgastvarvning</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2051,12 +2027,12 @@
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Insyn i affären</t>
+          <t>Snabbare felanmälan vinner</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Titta på ett dolt kort hos en motståndare.</t>
+          <t>Hyresgästen tröttnar på konkurrentens service och flyttar till er. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
@@ -2074,7 +2050,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>kika</t>
+          <t>hyresgastvarvning</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2085,12 +2061,12 @@
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Bra rykte i huset</t>
+          <t>Bättre läge, samma hyra</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Titta på ett dolt kort hos en motståndare.</t>
+          <t>Er fastighet erbjuder mer för pengarna och hyresgästen byter. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
@@ -2108,7 +2084,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>kika</t>
+          <t>hyresgastvarvning</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2119,12 +2095,12 @@
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Läckt information</t>
+          <t>Förnyelse med nya ytor</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Titta på ett dolt kort hos en motståndare.</t>
+          <t>Ni erbjuder en anpassad yta som konkurrenten inte kan matcha. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
@@ -2142,7 +2118,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>hyresgastvarvning</t>
+          <t>headhunting</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2153,12 +2129,12 @@
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Bättre villkor lockar över hyresgästen</t>
+          <t>Ni värvar deras bästa förvaltare</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>En hyresgäst hos en konkurrent flyttar till er efter ett bättre erbjudande. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
+          <t>En nyckelperson hos en konkurrent tackar ja till ert erbjudande. Ta ett slumpvis personkort från en motspelares hand.</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
@@ -2176,7 +2152,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>hyresgastvarvning</t>
+          <t>headhunting</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2187,12 +2163,12 @@
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Vi tar ankarhyresgästen</t>
+          <t>Konsulten byter uppdragsgivare</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Er uthyrare vinner en stor hyresgäst som konkurrenten räknat med. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
+          <t>Konkurrentens konsult går över till er mitt i uppdraget. Ta ett slumpvis personkort från en motspelares hand.</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
@@ -2210,7 +2186,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>hyresgastvarvning</t>
+          <t>headhunting</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2221,12 +2197,12 @@
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Flytterbjudande med hyresrabatt</t>
+          <t>Rekryteringsfirman hittar rätt</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Tre månaders rabatt räcker för att hyresgästen byter hyresvärd. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
+          <t>Headhuntern hittar exakt den person ni behöver — hos en konkurrent. Ta ett slumpvis personkort från en motspelares hand.</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
@@ -2244,7 +2220,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>hyresgastvarvning</t>
+          <t>dra_personkort</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2255,12 +2231,12 @@
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Snabbare felanmälan vinner</t>
+          <t>Ny kontakt knuten</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Hyresgästen tröttnar på konkurrentens service och flyttar till er. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
+          <t>Dra ett personkort.</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
@@ -2278,7 +2254,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>hyresgastvarvning</t>
+          <t>dra_personkort</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2289,12 +2265,12 @@
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Bättre läge, samma hyra</t>
+          <t>Rekommendation från kollega</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Er fastighet erbjuder mer för pengarna och hyresgästen byter. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
+          <t>Dra ett personkort.</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
@@ -2312,7 +2288,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>hyresgastvarvning</t>
+          <t>dra_personkort</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2323,12 +2299,12 @@
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Förnyelse med nya ytor</t>
+          <t>Nätverksträff</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Ni erbjuder en anpassad yta som konkurrenten inte kan matcha. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
+          <t>Dra ett personkort.</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
@@ -2346,7 +2322,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>headhunting</t>
+          <t>dra_personkort</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2357,12 +2333,12 @@
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Ni värvar deras bästa förvaltare</t>
+          <t>Gammal bekant hör av sig</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>En nyckelperson hos en konkurrent tackar ja till ert erbjudande. Ta ett slumpvis personkort från en motspelares hand.</t>
+          <t>Dra ett personkort.</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
@@ -2380,7 +2356,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>headhunting</t>
+          <t>dra_personkort</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2391,12 +2367,12 @@
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Konsulten byter uppdragsgivare</t>
+          <t>Tips vid kaffeautomaten</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Konkurrentens konsult går över till er mitt i uppdraget. Ta ett slumpvis personkort från en motspelares hand.</t>
+          <t>Dra ett personkort.</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
@@ -2414,7 +2390,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>headhunting</t>
+          <t>riskbuffert</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2425,12 +2401,12 @@
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Rekryteringsfirman hittar rätt</t>
+          <t>Extra marginal budgeterad</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Headhuntern hittar exakt den person ni behöver — hos en konkurrent. Ta ett slumpvis personkort från en motspelares hand.</t>
+          <t>Ta en riskbuffert.</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
@@ -2448,7 +2424,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>dra_personkort</t>
+          <t>riskbuffert</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2459,12 +2435,12 @@
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Ny kontakt knuten</t>
+          <t>Buffert i god tid</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Dra ett personkort.</t>
+          <t>Ta en riskbuffert.</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
@@ -2482,7 +2458,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>dra_personkort</t>
+          <t>riskbuffert</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2493,12 +2469,12 @@
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Rekommendation från kollega</t>
+          <t>Försiktig planering</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Dra ett personkort.</t>
+          <t>Ta en riskbuffert.</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
@@ -2516,7 +2492,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>dra_personkort</t>
+          <t>riskbuffert</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2527,12 +2503,12 @@
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Nätverksträff</t>
+          <t>Extra kapital avsatt</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Dra ett personkort.</t>
+          <t>Ta en riskbuffert.</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
@@ -2550,7 +2526,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>dra_personkort</t>
+          <t>utveckling</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2561,12 +2537,12 @@
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Gammal bekant hör av sig</t>
+          <t>Intern ledarutbildning</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Dra ett personkort.</t>
+          <t>FC eller FS går en intern ledarutbildning. Lägg en utvecklingsbricka på din FC eller FS.</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
@@ -2584,7 +2560,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>dra_personkort</t>
+          <t>utveckling</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2595,12 +2571,12 @@
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Tips vid kaffeautomaten</t>
+          <t>Branschcertifiering</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Dra ett personkort.</t>
+          <t>Er förvaltningschef tar en eftertraktad certifiering. Lägg en utvecklingsbricka på din FC eller FS.</t>
         </is>
       </c>
       <c r="H61" s="2" t="n">
@@ -2618,7 +2594,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>riskbuffert</t>
+          <t>utveckling</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2629,12 +2605,12 @@
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Extra marginal budgeterad</t>
+          <t>Mentorprogram</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Ta en riskbuffert.</t>
+          <t>Erfaren kollega delar med sig av sina knep. Lägg en utvecklingsbricka på din FC eller FS.</t>
         </is>
       </c>
       <c r="H62" s="2" t="n">
@@ -2652,7 +2628,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>riskbuffert</t>
+          <t>lagg_energi_plus_egen</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2663,12 +2639,12 @@
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Buffert i god tid</t>
+          <t>Injustering av värmesystemet</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Ta en riskbuffert.</t>
+          <t>Värmen balanseras om och radiatorerna slutar gå för fullt. Lägg en dold energiplusbricka på en egen fastighet.</t>
         </is>
       </c>
       <c r="H63" s="2" t="n">
@@ -2686,7 +2662,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>riskbuffert</t>
+          <t>lagg_energi_plus_egen</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2697,12 +2673,12 @@
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Försiktig planering</t>
+          <t>Solceller på taket</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Ta en riskbuffert.</t>
+          <t>Taket får solceller som täcker en del av fastighetselen. Lägg en dold energiplusbricka på en egen fastighet.</t>
         </is>
       </c>
       <c r="H64" s="2" t="n">
@@ -2720,7 +2696,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>riskbuffert</t>
+          <t>lagg_energi_plus_egen</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2731,12 +2707,12 @@
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Extra kapital avsatt</t>
+          <t>Tilläggsisolering av vinden</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Ta en riskbuffert.</t>
+          <t>Vindsbjälklaget isoleras och värmeförlusten minskar. Lägg en dold energiplusbricka på en egen fastighet.</t>
         </is>
       </c>
       <c r="H65" s="2" t="n">
@@ -2754,7 +2730,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>utveckling</t>
+          <t>lagg_energi_plus_egen</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2765,12 +2741,12 @@
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Intern ledarutbildning</t>
+          <t>Byte till LED i allmänna ytor</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>FC eller FS går en intern ledarutbildning. Lägg en utvecklingsbricka på din FC eller FS.</t>
+          <t>Trapphus och garage får ny belysning med närvarostyrning. Lägg en dold energiplusbricka på en egen fastighet.</t>
         </is>
       </c>
       <c r="H66" s="2" t="n">
@@ -2788,7 +2764,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>utveckling</t>
+          <t>lagg_energi_plus_egen</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2799,12 +2775,12 @@
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Branschcertifiering</t>
+          <t>Frånluftsvärmepump installeras</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Er förvaltningschef tar en eftertraktad certifiering. Lägg en utvecklingsbricka på din FC eller FS.</t>
+          <t>Värmen i frånluften tas tillvara i stället för att blåsa ut. Lägg en dold energiplusbricka på en egen fastighet.</t>
         </is>
       </c>
       <c r="H67" s="2" t="n">
@@ -2822,7 +2798,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>utveckling</t>
+          <t>direkt_dn_plus_egen</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2833,12 +2809,12 @@
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Mentorprogram</t>
+          <t>Genombrott i hyresförhandlingen</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Erfaren kollega delar med sig av sina knep. Lägg en utvecklingsbricka på din FC eller FS.</t>
+          <t>Ett nytt avtal höjer hyresnivån på en hel fastighet. +1 DN direkt och permanent på en egen fastighet.</t>
         </is>
       </c>
       <c r="H68" s="2" t="n">
@@ -2856,23 +2832,27 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>lagg_energi_plus_egen</t>
+          <t>budstrid</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>nar_som_helst</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr"/>
+          <t>vid_bud</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Injustering av värmesystemet</t>
+          <t>Säljaren behöver likviditet</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Värmen balanseras om och radiatorerna slutar gå för fullt. Lägg en dold energiplusbricka på en egen fastighet.</t>
+          <t>Ditt tvångsbud kostar 1,1 × MV i stället för 1,2 × MV. Spelas när du lägger budet.</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
@@ -2890,23 +2870,27 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>lagg_energi_plus_egen</t>
+          <t>budstrid</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>nar_som_helst</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr"/>
+          <t>vid_bud</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Solceller på taket</t>
+          <t>Kall kalkyl</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Taket får solceller som täcker en del av fastighetselen. Lägg en dold energiplusbricka på en egen fastighet.</t>
+          <t>Ditt tvångsbud kostar 1,1 × MV i stället för 1,2 × MV. Spelas när du lägger budet.</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
@@ -2924,23 +2908,27 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>lagg_energi_plus_egen</t>
+          <t>budstrid</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>nar_som_helst</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr"/>
+          <t>vid_bud</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Tilläggsisolering av vinden</t>
+          <t>Pressat läge hos motparten</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Vindsbjälklaget isoleras och värmeförlusten minskar. Lägg en dold energiplusbricka på en egen fastighet.</t>
+          <t>Ditt tvångsbud kostar 1,1 × MV i stället för 1,2 × MV. Spelas när du lägger budet.</t>
         </is>
       </c>
       <c r="H71" s="2" t="n">
@@ -2958,23 +2946,23 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>lagg_energi_plus_egen</t>
+          <t>overtagande</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>nar_som_helst</t>
+          <t>vid_bud</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Byte till LED i allmänna ytor</t>
+          <t>Juridiskt vattentätt</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Trapphus och garage får ny belysning med närvarostyrning. Lägg en dold energiplusbricka på en egen fastighet.</t>
+          <t>Ditt tvångsbud kan inte stoppas — varken med stoppkort eller riskbuffertar. Spelas när du lägger budet.</t>
         </is>
       </c>
       <c r="H72" s="2" t="n">
@@ -2992,23 +2980,23 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>lagg_energi_plus_egen</t>
+          <t>overtagande</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>nar_som_helst</t>
+          <t>vid_bud</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Frånluftsvärmepump installeras</t>
+          <t>Majoriteten i styrelsen</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Värmen i frånluften tas tillvara i stället för att blåsa ut. Lägg en dold energiplusbricka på en egen fastighet.</t>
+          <t>Ditt tvångsbud kan inte stoppas — varken med stoppkort eller riskbuffertar. Spelas när du lägger budet.</t>
         </is>
       </c>
       <c r="H73" s="2" t="n">
@@ -3026,7 +3014,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>direkt_dn_plus_egen</t>
+          <t>gratis_uppgradering</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3037,15 +3025,303 @@
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Genombrott i hyresförhandlingen</t>
+          <t>Totalentreprenad klar</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Ett nytt avtal höjer hyresnivån på en hel fastighet. +1 DN direkt och permanent på en egen fastighet.</t>
+          <t>Höj energiklassen ett steg på en egen fastighet — utan slag och utan kostnad.</t>
         </is>
       </c>
       <c r="H74" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>PK-74</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>gratis_uppgradering</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>nar_som_helst</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Fjärrvärmen konverteras</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Höj energiklassen ett steg på en egen fastighet — utan slag och utan kostnad.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>PK-75</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>gratis_uppgradering</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>nar_som_helst</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Energibolaget bjuder på åtgärden</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Höj energiklassen ett steg på en egen fastighet — utan slag och utan kostnad.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>PK-76</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>omforhandlat_lan</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>nar_som_helst</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Ny bank lockar</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Sänk räntan på en egen fastighet med 1 Mkr/år för resten av spelet (DN +1, marknadsvärdet oförändrat).</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>PK-77</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>omforhandlat_lan</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>nar_som_helst</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Grön obligation</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Sänk räntan på en egen fastighet med 1 Mkr/år för resten av spelet (DN +1, marknadsvärdet oförändrat).</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>PK-78</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>omforhandlat_lan</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>nar_som_helst</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Räntebindning i rätt läge</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Sänk räntan på en egen fastighet med 1 Mkr/år för resten av spelet (DN +1, marknadsvärdet oförändrat).</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>PK-79</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>dd_val</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>vid_kop</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Grundlig besiktning</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>När du köper en fastighet (även tvångsköp): dra två DD-kort och välj vilket som gäller.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>PK-80</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>dd_val</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>vid_kop</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Due diligence-team</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>När du köper en fastighet (även tvångsköp): dra två DD-kort och välj vilket som gäller.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>PK-81</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>konvertering</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>nar_som_helst</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Kontor blir bostäder</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Betala 5 Mkr: en egen lokal eller ett eget kontor byggs om till hyresrätt och följer bostadsspåret i yieldbanan. DN och energiklass behålls.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3096,7 +3372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3202,7 +3478,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Starkt kontaktnät</t>
+          <t>Inhyrd jurist</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3217,7 +3493,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Inhyrd jurist</t>
+          <t>Branschens bäste</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3232,7 +3508,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Övertaget läge</t>
+          <t>Signerat på plats</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3247,7 +3523,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Branschens bäste</t>
+          <t>Oemotståndligt bud</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3262,7 +3538,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Motpartens svaghet</t>
+          <t>Fast handslag</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3277,7 +3553,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Signerat på plats</t>
+          <t>Bättre isolering</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3292,7 +3568,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Oemotståndligt bud</t>
+          <t>Injusterat system</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3307,7 +3583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fast handslag</t>
+          <t>Energikonsult inhyrd</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3322,7 +3598,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bättre isolering</t>
+          <t>Erfaren installatör</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3337,7 +3613,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Injusterat system</t>
+          <t>Statligt stöd hittat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3352,7 +3628,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Extra timme på plats</t>
+          <t>Certifierad expert</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3367,7 +3643,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rätt verktyg</t>
+          <t>Helhetslösning levererad</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3382,7 +3658,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Energikonsult inhyrd</t>
+          <t>Dold förbättring</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3397,7 +3673,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Erfaren installatör</t>
+          <t>Tyst uppgradering</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3412,7 +3688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Statligt stöd hittat</t>
+          <t>Extra underhåll</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3427,7 +3703,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Noggrann besiktning</t>
+          <t>Kvalitetshöjning</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3442,7 +3718,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Certifierad expert</t>
+          <t>Diskret investering</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3457,7 +3733,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Helhetslösning levererad</t>
+          <t>Renoverat i tysthet</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3472,7 +3748,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dold förbättring</t>
+          <t>Fastighetsskötarens tips</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3487,7 +3763,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tyst uppgradering</t>
+          <t>Väl skött förvaltning</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3502,7 +3778,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Extra underhåll</t>
+          <t>Problemet är löst</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3517,7 +3793,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kvalitetshöjning</t>
+          <t>Snabb insats</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3532,7 +3808,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Diskret investering</t>
+          <t>Städat upp</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3547,7 +3823,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Renoverat i tysthet</t>
+          <t>Åtgärdat i tid</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3562,7 +3838,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fastighetsskötarens tips</t>
+          <t>Krisen avvärjd</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3577,7 +3853,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Väl skött förvaltning</t>
+          <t>Rent bord igen</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3592,7 +3868,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Problemet är löst</t>
+          <t>Hembudsrätt använd</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3607,7 +3883,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Snabb insats</t>
+          <t>Motbud i sista minuten</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3622,7 +3898,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Städat upp</t>
+          <t>Låst avtal</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3637,7 +3913,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Åtgärdat i tid</t>
+          <t>Styrelsen säger nej</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3652,7 +3928,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Krisen avvärjd</t>
+          <t>Juridiskt hinder</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3667,7 +3943,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rent bord igen</t>
+          <t>Tips från branschen</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3682,7 +3958,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hembudsrätt använd</t>
+          <t>Insyn i affären</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3697,7 +3973,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Motbud i sista minuten</t>
+          <t>Bra rykte i huset</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3712,7 +3988,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Låst avtal</t>
+          <t>Läckt information</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3727,7 +4003,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Styrelsen säger nej</t>
+          <t>Bättre villkor lockar över hyresgästen</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3742,7 +4018,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Juridiskt hinder</t>
+          <t>Vi tar ankarhyresgästen</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3757,7 +4033,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tips från branschen</t>
+          <t>Flytterbjudande med hyresrabatt</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3772,7 +4048,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Insyn i affären</t>
+          <t>Snabbare felanmälan vinner</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3787,7 +4063,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bra rykte i huset</t>
+          <t>Bättre läge, samma hyra</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3802,7 +4078,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Läckt information</t>
+          <t>Förnyelse med nya ytor</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3817,7 +4093,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bättre villkor lockar över hyresgästen</t>
+          <t>Ni värvar deras bästa förvaltare</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3832,7 +4108,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vi tar ankarhyresgästen</t>
+          <t>Konsulten byter uppdragsgivare</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3847,7 +4123,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Flytterbjudande med hyresrabatt</t>
+          <t>Rekryteringsfirman hittar rätt</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3862,7 +4138,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Snabbare felanmälan vinner</t>
+          <t>Ny kontakt knuten</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3877,7 +4153,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bättre läge, samma hyra</t>
+          <t>Rekommendation från kollega</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3892,7 +4168,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Förnyelse med nya ytor</t>
+          <t>Nätverksträff</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3907,7 +4183,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ni värvar deras bästa förvaltare</t>
+          <t>Gammal bekant hör av sig</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3922,7 +4198,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Konsulten byter uppdragsgivare</t>
+          <t>Tips vid kaffeautomaten</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3937,7 +4213,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rekryteringsfirman hittar rätt</t>
+          <t>Extra marginal budgeterad</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3952,7 +4228,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ny kontakt knuten</t>
+          <t>Buffert i god tid</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3967,7 +4243,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rekommendation från kollega</t>
+          <t>Försiktig planering</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3982,7 +4258,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nätverksträff</t>
+          <t>Extra kapital avsatt</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3997,7 +4273,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gammal bekant hör av sig</t>
+          <t>Intern ledarutbildning</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4012,7 +4288,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tips vid kaffeautomaten</t>
+          <t>Branschcertifiering</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4027,7 +4303,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Extra marginal budgeterad</t>
+          <t>Mentorprogram</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4042,7 +4318,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Buffert i god tid</t>
+          <t>Injustering av värmesystemet</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4057,7 +4333,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Försiktig planering</t>
+          <t>Solceller på taket</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4072,7 +4348,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Extra kapital avsatt</t>
+          <t>Tilläggsisolering av vinden</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4087,7 +4363,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Intern ledarutbildning</t>
+          <t>Byte till LED i allmänna ytor</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4102,7 +4378,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Branschcertifiering</t>
+          <t>Frånluftsvärmepump installeras</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4117,7 +4393,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mentorprogram</t>
+          <t>Genombrott i hyresförhandlingen</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4132,7 +4408,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Injustering av värmesystemet</t>
+          <t>Säljaren behöver likviditet</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4147,7 +4423,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Solceller på taket</t>
+          <t>Kall kalkyl</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4162,7 +4438,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tilläggsisolering av vinden</t>
+          <t>Pressat läge hos motparten</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4177,7 +4453,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Byte till LED i allmänna ytor</t>
+          <t>Juridiskt vattentätt</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4192,7 +4468,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Frånluftsvärmepump installeras</t>
+          <t>Majoriteten i styrelsen</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4207,10 +4483,130 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Genombrott i hyresförhandlingen</t>
+          <t>Totalentreprenad klar</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
+        <is>
+          <t>ej bestämt</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Fjärrvärmen konverteras</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ej bestämt</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Energibolaget bjuder på åtgärden</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ej bestämt</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Ny bank lockar</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ej bestämt</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Grön obligation</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ej bestämt</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Räntebindning i rätt läge</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ej bestämt</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Grundlig besiktning</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ej bestämt</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Due diligence-team</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ej bestämt</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Kontor blir bostäder</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
         <is>
           <t>ej bestämt</t>
         </is>
@@ -4484,7 +4880,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>73 (kortspecen: 73)</t>
+          <t>81 (kortspecen: 81)</t>
         </is>
       </c>
     </row>

--- a/kortdata/F_personkort.xlsx
+++ b/kortdata/F_personkort.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3322,6 +3322,74 @@
         </is>
       </c>
       <c r="H82" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>PK-82</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>motbud</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>reaktivt</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Motbud — vi köper er i stället</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Stoppa ett tvångsbud mot dig. Du får dessutom köpa en av budgivarens fastigheter till 1,0 × MV (valfritt).</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>PK-83</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>motbud</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>reaktivt</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Pac-Man-försvaret</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Stoppa ett tvångsbud mot dig. Du får dessutom köpa en av budgivarens fastigheter till 1,0 × MV (valfritt).</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3372,7 +3440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4607,6 +4675,36 @@
         </is>
       </c>
       <c r="C82" t="inlineStr">
+        <is>
+          <t>ej bestämt</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Motbud — vi köper er i stället</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ej bestämt</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Pac-Man-försvaret</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
         <is>
           <t>ej bestämt</t>
         </is>
@@ -4880,7 +4978,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>81 (kortspecen: 81)</t>
+          <t>83 (kortspecen: 83)</t>
         </is>
       </c>
     </row>
